--- a/artfynd/A 13604-2025 artfynd.xlsx
+++ b/artfynd/A 13604-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>107354965</v>
       </c>
       <c r="B2" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490856.6685807196</v>
+        <v>490857</v>
       </c>
       <c r="R2" t="n">
-        <v>6277642.403320638</v>
+        <v>6277642</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2023-03-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
